--- a/benchmark/functional/powdataflow/dataflow-measurements.xlsx
+++ b/benchmark/functional/powdataflow/dataflow-measurements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andiderp/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89621A02-AE2F-A44D-8214-8BBCE50C75A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E457C55E-078A-404D-9F61-CA319C5F6C81}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="1800" windowWidth="28040" windowHeight="17440" activeTab="5" xr2:uid="{C47F41CB-B47E-0148-87C7-130387C9F0E8}"/>
+    <workbookView xWindow="19480" yWindow="660" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{C47F41CB-B47E-0148-87C7-130387C9F0E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Formulog" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
   <si>
     <t>Ex1 (ms)</t>
   </si>
@@ -74,6 +74,42 @@
   </si>
   <si>
     <t>Ex4 Insert (ms)</t>
+  </si>
+  <si>
+    <t>Ex1 real (ms)</t>
+  </si>
+  <si>
+    <t>Ex1 user (ms)</t>
+  </si>
+  <si>
+    <t>Ex1 sys (ms)</t>
+  </si>
+  <si>
+    <t>Ex2 real (ms)</t>
+  </si>
+  <si>
+    <t>Ex2 user (ms)</t>
+  </si>
+  <si>
+    <t>Ex2 sys (ms)</t>
+  </si>
+  <si>
+    <t>Ex3 real (ms)</t>
+  </si>
+  <si>
+    <t>Ex3 user (ms)</t>
+  </si>
+  <si>
+    <t>Ex3 sys (ms)</t>
+  </si>
+  <si>
+    <t>Ex4 real (ms)</t>
+  </si>
+  <si>
+    <t>Ex4 user (ms)</t>
+  </si>
+  <si>
+    <t>Ex4 sys (ms)</t>
   </si>
 </sst>
 </file>
@@ -1858,21 +1894,425 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E3DE85-AD94-AB43-91C3-A301AEC98FD3}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>247</v>
+      </c>
+      <c r="B2">
+        <v>19</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>248</v>
+      </c>
+      <c r="E2">
+        <v>87</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>240</v>
+      </c>
+      <c r="H2">
+        <v>23</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>265</v>
+      </c>
+      <c r="K2">
+        <v>73</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>16</v>
+      </c>
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D3">
+        <v>93</v>
+      </c>
+      <c r="E3">
+        <v>88</v>
+      </c>
+      <c r="F3">
         <v>3</v>
+      </c>
+      <c r="G3">
+        <v>24</v>
+      </c>
+      <c r="H3">
+        <v>21</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>77</v>
+      </c>
+      <c r="K3">
+        <v>73</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>93</v>
+      </c>
+      <c r="E4">
+        <v>89</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>24</v>
+      </c>
+      <c r="H4">
+        <v>21</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>79</v>
+      </c>
+      <c r="K4">
+        <v>74</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>94</v>
+      </c>
+      <c r="E5">
+        <v>89</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>24</v>
+      </c>
+      <c r="H5">
+        <v>21</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>81</v>
+      </c>
+      <c r="K5">
+        <v>75</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>96</v>
+      </c>
+      <c r="E6">
+        <v>91</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>21</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>117</v>
+      </c>
+      <c r="K6">
+        <v>96</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>97</v>
+      </c>
+      <c r="E7">
+        <v>91</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>21</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>109</v>
+      </c>
+      <c r="K7">
+        <v>89</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>94</v>
+      </c>
+      <c r="E8">
+        <v>89</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>21</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>85</v>
+      </c>
+      <c r="K8">
+        <v>78</v>
+      </c>
+      <c r="L8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>16</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>94</v>
+      </c>
+      <c r="E9">
+        <v>89</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>24</v>
+      </c>
+      <c r="H9">
+        <v>21</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>85</v>
+      </c>
+      <c r="K9">
+        <v>78</v>
+      </c>
+      <c r="L9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>16</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>97</v>
+      </c>
+      <c r="E10">
+        <v>91</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>24</v>
+      </c>
+      <c r="H10">
+        <v>21</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>93</v>
+      </c>
+      <c r="K10">
+        <v>82</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>97</v>
+      </c>
+      <c r="E11">
+        <v>90</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
+        <v>24</v>
+      </c>
+      <c r="H11">
+        <v>21</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>87</v>
+      </c>
+      <c r="K11">
+        <v>79</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1882,20 +2322,427 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65CCEC3C-B1DC-7141-A7D8-9D622D2B31EC}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>19</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>147</v>
+      </c>
+      <c r="E2">
+        <v>128</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>252</v>
+      </c>
+      <c r="H2">
+        <v>45</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>246</v>
+      </c>
+      <c r="K2">
+        <v>52</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>21</v>
+      </c>
+      <c r="B3">
+        <v>18</v>
+      </c>
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D3">
+        <v>120</v>
+      </c>
+      <c r="E3">
+        <v>114</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>49</v>
+      </c>
+      <c r="H3">
+        <v>44</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>56</v>
+      </c>
+      <c r="K3">
+        <v>52</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>120</v>
+      </c>
+      <c r="E4">
+        <v>115</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>50</v>
+      </c>
+      <c r="H4">
+        <v>45</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>56</v>
+      </c>
+      <c r="K4">
+        <v>52</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>21</v>
+      </c>
+      <c r="B5">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>122</v>
+      </c>
+      <c r="E5">
+        <v>116</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>45</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>58</v>
+      </c>
+      <c r="K5">
+        <v>52</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>21</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>116</v>
+      </c>
+      <c r="E6">
+        <v>112</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>45</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>56</v>
+      </c>
+      <c r="K6">
+        <v>51</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>117</v>
+      </c>
+      <c r="E7">
+        <v>113</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>49</v>
+      </c>
+      <c r="H7">
+        <v>44</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>59</v>
+      </c>
+      <c r="K7">
+        <v>53</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>21</v>
+      </c>
+      <c r="B8">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>119</v>
+      </c>
+      <c r="E8">
+        <v>114</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>48</v>
+      </c>
+      <c r="H8">
+        <v>44</v>
+      </c>
+      <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8">
+        <v>59</v>
+      </c>
+      <c r="K8">
+        <v>53</v>
+      </c>
+      <c r="L8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>21</v>
+      </c>
+      <c r="B9">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>120</v>
+      </c>
+      <c r="E9">
+        <v>115</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>49</v>
+      </c>
+      <c r="H9">
+        <v>45</v>
+      </c>
+      <c r="I9">
+        <v>3</v>
+      </c>
+      <c r="J9">
+        <v>62</v>
+      </c>
+      <c r="K9">
+        <v>55</v>
+      </c>
+      <c r="L9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>22</v>
+      </c>
+      <c r="B10">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>118</v>
+      </c>
+      <c r="E10">
+        <v>113</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>49</v>
+      </c>
+      <c r="H10">
+        <v>44</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <v>60</v>
+      </c>
+      <c r="K10">
+        <v>53</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>21</v>
+      </c>
+      <c r="B11">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>117</v>
+      </c>
+      <c r="E11">
+        <v>112</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>52</v>
+      </c>
+      <c r="H11">
+        <v>46</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>59</v>
+      </c>
+      <c r="K11">
+        <v>53</v>
+      </c>
+      <c r="L11">
         <v>3</v>
       </c>
     </row>

--- a/benchmark/functional/powdataflow/dataflow-measurements.xlsx
+++ b/benchmark/functional/powdataflow/dataflow-measurements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10614"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andiderp/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/home/projects/inca/benchmark/functional/powdataflow/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E457C55E-078A-404D-9F61-CA319C5F6C81}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756B1564-15A6-7146-9050-979FDE4685C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19480" yWindow="660" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{C47F41CB-B47E-0148-87C7-130387C9F0E8}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="76800" windowHeight="42700" activeTab="6" xr2:uid="{C47F41CB-B47E-0148-87C7-130387C9F0E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Formulog" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,82 @@
     <sheet name="Fun Inca DRed" sheetId="4" r:id="rId4"/>
     <sheet name="Fun Inca DDF" sheetId="6" r:id="rId5"/>
     <sheet name="Fun Inca DDF no inline simple" sheetId="5" r:id="rId6"/>
+    <sheet name="PLOTS" sheetId="7" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'Fun Inca DRed'!$B$1</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'Fun Inca DRed'!$B$2:$B$101</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">'Fun Inca DDF no inline simple'!$E$1</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">'Fun Inca DDF no inline simple'!$E$2:$E$101</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">'Fun Inca DDF no inline simple'!$H$1</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">'Fun Inca DDF no inline simple'!$H$2:$H$101</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">'Fun Inca DDF no inline simple'!$K$1</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">'Fun Inca DDF no inline simple'!$K$2:$K$101</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">'Fun Inca DDF no inline simple'!$B$1</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">'Fun Inca DDF no inline simple'!$B$2:$B$101</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">'Fun Inca DDF no inline simple'!$E$1</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">'Fun Inca DDF no inline simple'!$E$2:$E$101</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'Fun Inca DRed'!$E$1</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">'Fun Inca DDF no inline simple'!$H$1</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">'Fun Inca DDF no inline simple'!$H$2:$H$101</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">'Fun Inca DDF no inline simple'!$K$1</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">'Fun Inca DDF no inline simple'!$K$2:$K$101</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">Souffle!$B$1</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">Souffle!$B$2:$B$11</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">Souffle!$E$1</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">Souffle!$E$2:$E$11</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">Souffle!$H$1</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">Souffle!$H$2:$H$11</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Fun Inca DRed'!$E$2:$E$101</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">Souffle!$K$1</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">Souffle!$K$2:$K$11</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">Formulog!$A$1</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">Formulog!$A$2:$A$101</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">Formulog!$B$1</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">Formulog!$B$2:$B$101</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">Formulog!$C$1</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">Formulog!$C$2:$C$101</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">Formulog!$D$1</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">Formulog!$D$2:$D$101</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'Fun Inca DRed'!$H$1</definedName>
+    <definedName name="_xlchart.v1.40" hidden="1">'Fun Inca DDF no inline simple'!$B$1</definedName>
+    <definedName name="_xlchart.v1.41" hidden="1">'Fun Inca DDF no inline simple'!$B$2:$B$101</definedName>
+    <definedName name="_xlchart.v1.42" hidden="1">'Fun Inca DDF no inline simple'!$E$1</definedName>
+    <definedName name="_xlchart.v1.43" hidden="1">'Fun Inca DDF no inline simple'!$E$2:$E$101</definedName>
+    <definedName name="_xlchart.v1.44" hidden="1">'Fun Inca DDF no inline simple'!$H$1</definedName>
+    <definedName name="_xlchart.v1.45" hidden="1">'Fun Inca DDF no inline simple'!$H$2:$H$101</definedName>
+    <definedName name="_xlchart.v1.46" hidden="1">'Fun Inca DDF no inline simple'!$K$1</definedName>
+    <definedName name="_xlchart.v1.47" hidden="1">'Fun Inca DDF no inline simple'!$K$2:$K$101</definedName>
+    <definedName name="_xlchart.v1.48" hidden="1">'Fun Inca -&gt; Souffle'!$B$1</definedName>
+    <definedName name="_xlchart.v1.49" hidden="1">'Fun Inca -&gt; Souffle'!$B$2:$B$11</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'Fun Inca DRed'!$H$2:$H$101</definedName>
+    <definedName name="_xlchart.v1.50" hidden="1">'Fun Inca -&gt; Souffle'!$E$1</definedName>
+    <definedName name="_xlchart.v1.51" hidden="1">'Fun Inca -&gt; Souffle'!$E$2:$E$11</definedName>
+    <definedName name="_xlchart.v1.52" hidden="1">'Fun Inca -&gt; Souffle'!$H$1</definedName>
+    <definedName name="_xlchart.v1.53" hidden="1">'Fun Inca -&gt; Souffle'!$H$2:$H$11</definedName>
+    <definedName name="_xlchart.v1.54" hidden="1">'Fun Inca -&gt; Souffle'!$K$1</definedName>
+    <definedName name="_xlchart.v1.55" hidden="1">'Fun Inca -&gt; Souffle'!$K$2:$K$11</definedName>
+    <definedName name="_xlchart.v1.56" hidden="1">Souffle!$B$1</definedName>
+    <definedName name="_xlchart.v1.57" hidden="1">Souffle!$B$2:$B$11</definedName>
+    <definedName name="_xlchart.v1.58" hidden="1">Souffle!$E$1</definedName>
+    <definedName name="_xlchart.v1.59" hidden="1">Souffle!$E$2:$E$11</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'Fun Inca DRed'!$K$1</definedName>
+    <definedName name="_xlchart.v1.60" hidden="1">Souffle!$H$1</definedName>
+    <definedName name="_xlchart.v1.61" hidden="1">Souffle!$H$2:$H$11</definedName>
+    <definedName name="_xlchart.v1.62" hidden="1">Souffle!$K$1</definedName>
+    <definedName name="_xlchart.v1.63" hidden="1">Souffle!$K$2:$K$11</definedName>
+    <definedName name="_xlchart.v1.64" hidden="1">'Fun Inca DRed'!$B$1</definedName>
+    <definedName name="_xlchart.v1.65" hidden="1">'Fun Inca DRed'!$B$2:$B$101</definedName>
+    <definedName name="_xlchart.v1.66" hidden="1">'Fun Inca DRed'!$E$1</definedName>
+    <definedName name="_xlchart.v1.67" hidden="1">'Fun Inca DRed'!$E$2:$E$101</definedName>
+    <definedName name="_xlchart.v1.68" hidden="1">'Fun Inca DRed'!$H$1</definedName>
+    <definedName name="_xlchart.v1.69" hidden="1">'Fun Inca DRed'!$H$2:$H$101</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">'Fun Inca DRed'!$K$2:$K$101</definedName>
+    <definedName name="_xlchart.v1.70" hidden="1">'Fun Inca DRed'!$K$1</definedName>
+    <definedName name="_xlchart.v1.71" hidden="1">'Fun Inca DRed'!$K$2:$K$101</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">'Fun Inca DDF no inline simple'!$B$1</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">'Fun Inca DDF no inline simple'!$B$2:$B$101</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -171,6 +246,3786 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.33</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.35</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.37</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.39</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Formulog</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>Formulog</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{A008A38C-95CB-8D45-A6C8-B5E62ED25C61}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.32</cx:f>
+              <cx:v>Ex1 (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{BDFBF60A-48ED-0543-B198-D394E43ED570}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.34</cx:f>
+              <cx:v>Ex2 (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{8287ACF4-F70C-004F-B4AC-8B88F6252ACF}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.36</cx:f>
+              <cx:v>Ex3 (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{17F9ECCE-92FE-304D-A3D5-0B2B2756F46A}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.38</cx:f>
+              <cx:v>Ex4 (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling max="400"/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.57</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.59</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.61</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.63</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Souffle</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>Souffle</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{6EB5F3D5-836D-8543-B00C-9114744C6999}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.56</cx:f>
+              <cx:v>Ex1 user (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{E6307A6C-18F3-3D49-98D7-4A5C16D29795}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.58</cx:f>
+              <cx:v>Ex2 user (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{D149C7C3-2946-DF45-9E7E-DE0B32DB5713}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.60</cx:f>
+              <cx:v>Ex3 user (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{1200FDDC-D2EB-5F4F-BDDC-29AA3880C708}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.62</cx:f>
+              <cx:v>Ex4 user (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling max="400"/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.49</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.51</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.53</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.55</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Fun Inca -&gt; Souffle</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>Fun Inca -&gt; Souffle</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{9DE3CF4C-71B6-5744-898E-DEB0A156351A}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.48</cx:f>
+              <cx:v>Ex1 user (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{3B3D2BFD-E764-734C-B005-52F599B63821}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.50</cx:f>
+              <cx:v>Ex2 user (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{6C600E59-D40C-B944-9C5C-E1715A7F6248}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.52</cx:f>
+              <cx:v>Ex3 user (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{4979F5D8-AF20-134B-A680-7F2B8C70DA0C}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.54</cx:f>
+              <cx:v>Ex4 user (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling max="400"/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx4.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.65</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.67</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.69</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.71</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Fun Inca DRed</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>Fun Inca DRed</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{E3D7FF2B-BBB8-D143-957A-85252608AFDC}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.64</cx:f>
+              <cx:v>Ex1 Insert (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{093F6B38-1C35-364D-A260-702288B931CE}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.66</cx:f>
+              <cx:v>Ex2 Insert (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{65723D3E-13EB-E841-9C3F-E225CA73C8E6}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.68</cx:f>
+              <cx:v>Ex3 Insert (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{161276D3-11DD-DC42-B514-535166BB10AF}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.70</cx:f>
+              <cx:v>Ex4 Insert (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling max="400"/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx5.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.41</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.43</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.45</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.47</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Fun Inca DDF no inline simple</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>Fun Inca DDF no inline simple</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{0EFB8478-40B3-5F4D-82C2-2F81317A1B8C}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.40</cx:f>
+              <cx:v>Ex1 Insert (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{7BE6E87A-95FD-FE4B-BA62-F702E7460D3C}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.42</cx:f>
+              <cx:v>Ex2 Insert (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{FB2C4DB3-AFE6-4D46-9E0F-039D3506717D}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.44</cx:f>
+              <cx:v>Ex3 Insert (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{E9B2C1A4-924D-634D-AAA7-0DC0CBFCC96A}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.46</cx:f>
+              <cx:v>Ex4 Insert (ms)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="0"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling max="400"/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>260350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>704850</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Chart 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DD8269C-920D-C143-8394-7B101A3BB5BC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="260350" y="359654"/>
+              <a:ext cx="4570206" cy="2711055"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>16575</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>149925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>461075</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>48325</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Chart 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B455BEE4-F08C-1043-AD29-2807D8FD5C3C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4967422" y="350829"/>
+              <a:ext cx="4570207" cy="2711055"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>717944</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>100452</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>339097</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>30997</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Chart 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5094054-B3B2-654E-8262-1A9FDD9C50FC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9794498" y="301356"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>523785</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>100452</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>144937</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>30997</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="Chart 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EAF46C7-FD73-6C40-811C-586DC661335C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="14551186" y="301356"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>272655</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114802</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>718949</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>45347</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="7" name="Chart 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A6F17C8-4578-3445-8FD3-756246D059CF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="19250904" y="315706"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10708,4 +14563,14 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FF8C915-57FA-2846-B9D0-07FEBC45C91E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>